--- a/artfynd/A 29135-2022 artfynd.xlsx
+++ b/artfynd/A 29135-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29135-2022 artfynd.xlsx
+++ b/artfynd/A 29135-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91489422</v>
+        <v>91489419</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485657.0651963154</v>
+        <v>485701</v>
       </c>
       <c r="R2" t="n">
-        <v>6992395.179628696</v>
+        <v>6992372</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91489419</v>
+        <v>91612650</v>
       </c>
       <c r="B3" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485701.0081756864</v>
+        <v>485647</v>
       </c>
       <c r="R3" t="n">
-        <v>6992371.859814622</v>
+        <v>6992373</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +844,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91489420</v>
+        <v>91489422</v>
       </c>
       <c r="B4" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485701.0081756864</v>
+        <v>485657</v>
       </c>
       <c r="R4" t="n">
-        <v>6992371.859814622</v>
+        <v>6992395</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91612649</v>
+        <v>91612652</v>
       </c>
       <c r="B5" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485646.9774959235</v>
+        <v>485647</v>
       </c>
       <c r="R5" t="n">
-        <v>6992373.004989694</v>
+        <v>6992373</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1096,19 +1046,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91612652</v>
+        <v>91489420</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485646.9774959235</v>
+        <v>485701</v>
       </c>
       <c r="R6" t="n">
-        <v>6992373.004989694</v>
+        <v>6992372</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,19 +1147,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91612650</v>
+        <v>91612649</v>
       </c>
       <c r="B7" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219795</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485646.9774959235</v>
+        <v>485647</v>
       </c>
       <c r="R7" t="n">
-        <v>6992373.004989694</v>
+        <v>6992373</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1328,19 +1248,9 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 29135-2022 artfynd.xlsx
+++ b/artfynd/A 29135-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91612650</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91612652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489420</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91612649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>